--- a/data/trans_orig/P44A$endoscopia-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P44A$endoscopia-Provincia-trans_orig.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16162</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,77%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>818</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>9338</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>51,81%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>11783</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21909</t>
+          <t>22006</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13964</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19646</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33609</t>
+          <t>33920</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>76,18%</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>7349</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>998</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>13398</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12721</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14141</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>8351</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22651</t>
+          <t>22283</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,04%</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7361</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17302</t>
+          <t>17570</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8487</t>
+          <t>8830</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2791</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7730</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18098</t>
+          <t>18145</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9572</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>53,5%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9743</t>
+          <t>10059</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11651</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9651</t>
+          <t>9629</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20252</t>
+          <t>20193</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,08%</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>12563</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>51,07%</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>4929</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>979</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7613</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>10541</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,85%</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>7554</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t>9599</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,62%</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>5455</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>42,41%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>13438</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,34%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>908</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10476</t>
+          <t>11373</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>73,19%</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>994</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>52,49%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>13611</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>8122</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>18199</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17549</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30093</t>
+          <t>30328</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,6%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>855</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14578</t>
+          <t>14579</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>5617</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15511</t>
+          <t>16012</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14293</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>27337</t>
+          <t>27641</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>76,19%</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12399</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14968</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17119</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>11789</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>11882</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>24754</t>
+          <t>25116</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,86%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15872</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>18147</t>
+          <t>18815</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>18938</t>
+          <t>19291</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,98%</t>
         </is>
       </c>
     </row>
@@ -4263,12 +4263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11742</t>
+          <t>11699</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9704</t>
+          <t>9641</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4313,12 +4313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>19165</t>
+          <t>18975</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4348,12 +4348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>57249</t>
+          <t>55486</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>77847</t>
+          <t>78290</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>55232</t>
+          <t>55119</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>76516</t>
+          <t>76255</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>117916</t>
+          <t>117157</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>147087</t>
+          <t>147876</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12508</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>30662</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>16111</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>19817</t>
+          <t>19570</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>40649</t>
+          <t>42080</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>30546</t>
+          <t>31229</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>53643</t>
+          <t>52413</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>24440</t>
+          <t>24308</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>45004</t>
+          <t>45114</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>60545</t>
+          <t>60319</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>90964</t>
+          <t>89254</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,26%</t>
         </is>
       </c>
     </row>
@@ -4719,12 +4719,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>27833</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4734,12 +4734,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>28103</t>
+          <t>27274</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>50006</t>
+          <t>47331</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>41755</t>
+          <t>42263</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>70122</t>
+          <t>69254</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12662</t>
+          <t>12830</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10174</t>
+          <t>10449</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19892</t>
+          <t>19573</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>49,99%</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14653</t>
+          <t>13863</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8187</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18233</t>
+          <t>18067</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13638</t>
+          <t>13668</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29346</t>
+          <t>29400</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13799</t>
+          <t>13825</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,02%</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3942</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>38,63%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>791</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>988</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>54,61%</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,42%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>12004</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>9809</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17945</t>
+          <t>18771</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>45,96%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11934</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15834</t>
+          <t>15614</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8554</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17951</t>
+          <t>17891</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18297</t>
+          <t>18250</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31276</t>
+          <t>30770</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>75,34%</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14315</t>
+          <t>14573</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>20557</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19454</t>
+          <t>19391</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25937</t>
+          <t>25988</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39609</t>
+          <t>38334</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7358</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>5759</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>8739</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12718</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10733</t>
+          <t>11002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20992</t>
+          <t>20745</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6779,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8487</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>6732</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6864,12 +6864,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,46%</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>991</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>85,89%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2446</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8593</t>
+          <t>9263</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14973</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6523</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>52,59%</t>
         </is>
       </c>
     </row>
@@ -7691,12 +7691,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>7974</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7726,12 +7726,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7761,12 +7761,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>11819</t>
+          <t>11991</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>63,14%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20470</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>32806</t>
+          <t>32759</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13492</t>
+          <t>13269</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23953</t>
+          <t>23882</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>37200</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>53981</t>
+          <t>54562</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>79,63%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14568</t>
+          <t>14298</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>9772</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19572</t>
+          <t>20184</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14857</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>27423</t>
+          <t>27484</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15177</t>
+          <t>15318</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>21848</t>
+          <t>21809</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>38554</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>56,27%</t>
         </is>
       </c>
     </row>
@@ -8147,12 +8147,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9619</t>
+          <t>8872</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8182,12 +8182,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>877</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8217,12 +8217,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13946</t>
+          <t>13762</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8232,12 +8232,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>16852</t>
+          <t>16396</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>10865</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>24101</t>
+          <t>24593</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>61,67%</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>12367</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>15392</t>
+          <t>15114</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>37,9%</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12545</t>
+          <t>12582</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9713</t>
+          <t>8850</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7183</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>19287</t>
+          <t>19361</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,55%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>69928</t>
+          <t>69918</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>95964</t>
+          <t>94738</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>52283</t>
+          <t>53034</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>76630</t>
+          <t>75580</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>131253</t>
+          <t>131008</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>165398</t>
+          <t>166096</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,22%</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26977</t>
+          <t>25970</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>15993</t>
+          <t>17587</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>18302</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>38486</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>47067</t>
+          <t>46341</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>71353</t>
+          <t>70995</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>28939</t>
+          <t>29060</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>51378</t>
+          <t>50732</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>80188</t>
+          <t>82236</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>113112</t>
+          <t>114733</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,6%</t>
         </is>
       </c>
     </row>
@@ -9059,12 +9059,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>26384</t>
+          <t>26818</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>47921</t>
+          <t>48850</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9074,12 +9074,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>21031</t>
+          <t>21083</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>40709</t>
+          <t>41399</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>52593</t>
+          <t>52459</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>82205</t>
+          <t>81742</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -9407,32 +9407,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22914</t>
+          <t>24459</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>18273</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>31697</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9442,32 +9442,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8685</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5157</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9477,32 +9477,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>31154</t>
+          <t>33143</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24189</t>
+          <t>26277</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39492</t>
+          <t>41880</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>38,18%</t>
         </is>
       </c>
     </row>
@@ -9520,32 +9520,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48761</t>
+          <t>47463</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41346</t>
+          <t>39996</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55275</t>
+          <t>53791</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9555,32 +9555,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27399</t>
+          <t>27973</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23613</t>
+          <t>24201</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30353</t>
+          <t>30990</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9590,32 +9590,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>76160</t>
+          <t>75436</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68033</t>
+          <t>66755</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83345</t>
+          <t>82981</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>75,65%</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9668,32 +9668,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>502</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9703,32 +9703,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -9863,32 +9863,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>21095</t>
+          <t>21794</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>14287</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28909</t>
+          <t>29353</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9898,32 +9898,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10658</t>
+          <t>11045</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20449</t>
+          <t>20382</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9933,32 +9933,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>36220</t>
+          <t>37368</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27940</t>
+          <t>28939</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45613</t>
+          <t>47930</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -9976,32 +9976,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50231</t>
+          <t>52779</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42736</t>
+          <t>45722</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55665</t>
+          <t>58137</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10011,32 +10011,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33456</t>
+          <t>35983</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29635</t>
+          <t>32177</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36503</t>
+          <t>39094</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10046,32 +10046,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>83686</t>
+          <t>88762</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>74965</t>
+          <t>80543</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>89958</t>
+          <t>95164</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,76%</t>
         </is>
       </c>
     </row>
@@ -10089,32 +10089,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21545</t>
+          <t>21707</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14698</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29486</t>
+          <t>29969</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10124,32 +10124,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>13399</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16852</t>
+          <t>18661</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10159,32 +10159,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>33508</t>
+          <t>35105</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24947</t>
+          <t>25972</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42156</t>
+          <t>44567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,57%</t>
         </is>
       </c>
     </row>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>723</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -10247,12 +10247,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>723</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -10282,12 +10282,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -10319,32 +10319,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23379</t>
+          <t>22721</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17344</t>
+          <t>16939</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29472</t>
+          <t>29004</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10354,32 +10354,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17553</t>
+          <t>17882</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12769</t>
+          <t>12967</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23122</t>
+          <t>23192</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10389,32 +10389,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>40933</t>
+          <t>40604</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>33476</t>
+          <t>32537</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>49107</t>
+          <t>48446</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>42,93%</t>
         </is>
       </c>
     </row>
@@ -10432,32 +10432,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35908</t>
+          <t>35294</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29283</t>
+          <t>29429</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41541</t>
+          <t>40821</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10467,32 +10467,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>41747</t>
+          <t>42575</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37112</t>
+          <t>37259</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46061</t>
+          <t>47171</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10502,32 +10502,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>77657</t>
+          <t>77869</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70134</t>
+          <t>69466</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84968</t>
+          <t>85205</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,51%</t>
         </is>
       </c>
     </row>
@@ -10545,32 +10545,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>9074</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10580,32 +10580,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10615,32 +10615,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10706</t>
+          <t>11382</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -10658,32 +10658,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>567</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10728,22 +10728,22 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>571</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -10775,32 +10775,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24586</t>
+          <t>28600</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18514</t>
+          <t>21600</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30690</t>
+          <t>35900</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10810,32 +10810,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>30137</t>
+          <t>32377</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24944</t>
+          <t>26926</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35494</t>
+          <t>38478</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>54723</t>
+          <t>60977</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46172</t>
+          <t>50712</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62867</t>
+          <t>69796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -10888,32 +10888,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32682</t>
+          <t>35407</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26225</t>
+          <t>28321</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38256</t>
+          <t>42550</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10923,32 +10923,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29844</t>
+          <t>32369</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24411</t>
+          <t>26436</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34655</t>
+          <t>38157</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10958,32 +10958,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>62526</t>
+          <t>67776</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>53678</t>
+          <t>58816</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70536</t>
+          <t>76841</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>62,53%</t>
         </is>
       </c>
     </row>
@@ -11001,32 +11001,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>561</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11036,32 +11036,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>516</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11071,32 +11071,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -11231,32 +11231,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9496</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6858</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11698</t>
+          <t>11933</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11266,32 +11266,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9223</t>
+          <t>9683</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11301,32 +11301,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>17110</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>13732</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19418</t>
+          <t>20623</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,97%</t>
         </is>
       </c>
     </row>
@@ -11344,32 +11344,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>4429</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11379,32 +11379,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10008</t>
+          <t>10513</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11414,32 +11414,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>11962</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15302</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -11457,32 +11457,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>474</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11492,32 +11492,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1547</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>391</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11527,32 +11527,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5930</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>520</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -11580,12 +11580,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>432</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>952</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -11687,32 +11687,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17008</t>
+          <t>16483</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>11768</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21979</t>
+          <t>20716</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11722,32 +11722,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6901</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10526</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11757,32 +11757,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>23909</t>
+          <t>23399</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>18061</t>
+          <t>17616</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29849</t>
+          <t>29501</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,84%</t>
         </is>
       </c>
     </row>
@@ -11800,32 +11800,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>23120</t>
+          <t>22450</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18150</t>
+          <t>17815</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27527</t>
+          <t>26879</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11835,32 +11835,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>24656</t>
+          <t>25103</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21009</t>
+          <t>21403</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27267</t>
+          <t>27638</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11870,32 +11870,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>47775</t>
+          <t>47553</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41733</t>
+          <t>41225</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53065</t>
+          <t>52797</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,67%</t>
         </is>
       </c>
     </row>
@@ -11913,32 +11913,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11948,32 +11948,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11983,32 +11983,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13570</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>375</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>375</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -12143,102 +12143,102 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>49236</t>
+          <t>58105</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>39182</t>
+          <t>46754</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>58346</t>
+          <t>68893</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>47,8%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>38,46%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>56,67%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>46477</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>38399</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>55754</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>34,49%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>28,5%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>41,37%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>104582</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>90628</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>119504</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>40,8%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>35,36%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>46,62%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>37,1%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>55,25%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>39496</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>32150</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>48643</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>34,61%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>28,18%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>42,63%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>88732</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>76706</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>101127</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>40,39%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>34,91%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>46,03%</t>
         </is>
       </c>
     </row>
@@ -12256,32 +12256,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>46271</t>
+          <t>52865</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>36322</t>
+          <t>43323</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>55497</t>
+          <t>63766</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12291,32 +12291,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>74693</t>
+          <t>88328</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>65191</t>
+          <t>79161</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>82426</t>
+          <t>97521</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12326,32 +12326,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>120965</t>
+          <t>141192</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>108856</t>
+          <t>127249</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>133672</t>
+          <t>156058</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,89%</t>
         </is>
       </c>
     </row>
@@ -12369,32 +12369,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>23651</t>
+          <t>26256</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>18338</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>31524</t>
+          <t>36384</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12404,32 +12404,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>12911</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>8292</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14583</t>
+          <t>19834</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12439,17 +12439,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>33566</t>
+          <t>39168</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25705</t>
+          <t>29141</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>43445</t>
+          <t>49676</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -12492,12 +12492,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>6679</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>660</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2462</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>6453</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -12599,32 +12599,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>302714</t>
+          <t>65352</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>159154</t>
+          <t>55107</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>354756</t>
+          <t>75438</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12634,32 +12634,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>49930</t>
+          <t>57052</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>42697</t>
+          <t>48811</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>58616</t>
+          <t>67179</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12669,32 +12669,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>352643</t>
+          <t>122405</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>200470</t>
+          <t>108487</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>461755</t>
+          <t>136258</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>46,5%</t>
         </is>
       </c>
     </row>
@@ -12712,32 +12712,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>347886</t>
+          <t>115554</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>288940</t>
+          <t>105635</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>366806</t>
+          <t>123408</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12747,32 +12747,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>98435</t>
+          <t>112265</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>90785</t>
+          <t>104079</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>105387</t>
+          <t>120454</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12782,32 +12782,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>446321</t>
+          <t>227820</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>386376</t>
+          <t>215550</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>487695</t>
+          <t>239072</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>81,58%</t>
         </is>
       </c>
     </row>
@@ -12825,32 +12825,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>254993</t>
+          <t>12390</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>23721</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>341719</t>
+          <t>20405</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12860,32 +12860,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>22105</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16585</t>
+          <t>19141</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>29713</t>
+          <t>32819</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12895,32 +12895,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>277098</t>
+          <t>37640</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>57465</t>
+          <t>28945</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>432144</t>
+          <t>48324</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -13055,32 +13055,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>470429</t>
+          <t>247403</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>324645</t>
+          <t>224008</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>638546</t>
+          <t>268391</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13090,32 +13090,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>174304</t>
+          <t>192185</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>159143</t>
+          <t>176466</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>189444</t>
+          <t>209550</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13125,32 +13125,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>644732</t>
+          <t>439588</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>488561</t>
+          <t>413953</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>939193</t>
+          <t>465238</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -13168,32 +13168,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>589045</t>
+          <t>366242</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>491588</t>
+          <t>344945</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>699871</t>
+          <t>388744</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13203,32 +13203,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>338007</t>
+          <t>372902</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>323663</t>
+          <t>356019</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>351987</t>
+          <t>388187</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13238,32 +13238,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>927052</t>
+          <t>739144</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>840970</t>
+          <t>713361</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1087759</t>
+          <t>763640</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>69,48%</t>
         </is>
       </c>
     </row>
@@ -13281,32 +13281,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>315969</t>
+          <t>76147</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>96806</t>
+          <t>61756</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>574811</t>
+          <t>94022</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13316,32 +13316,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>53924</t>
+          <t>62077</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>44454</t>
+          <t>51114</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>64367</t>
+          <t>73872</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13351,32 +13351,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>369892</t>
+          <t>138224</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>148812</t>
+          <t>120008</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>786892</t>
+          <t>155990</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -13394,32 +13394,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>8062</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -13429,22 +13429,22 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -13464,32 +13464,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>12210</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
